--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 88 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 87 clubs short</t>
         </is>
       </c>
     </row>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3216,8 +3216,8 @@
       <c r="S26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="9" t="n">
-        <v>0</v>
+      <c r="T26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="10" t="n">
         <v>2</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6894,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -17526,7 +17526,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -17757,7 +17757,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 87 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 82 clubs short</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2555,8 +2555,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5450,8 +5450,8 @@
       <c r="T49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
+      <c r="U49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V49" s="9" t="n">
         <v>2</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12643,8 +12643,8 @@
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12832,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12922,11 +12922,11 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>3</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" s="9" t="n">
         <v>3</v>
@@ -17460,7 +17460,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17493,7 +17493,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17592,7 +17592,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17691,7 +17691,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17724,7 +17724,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18252,7 +18252,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -18285,7 +18285,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 82 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA171"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1276,8 +1276,8 @@
       <c r="S6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3313,8 +3313,8 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4204,8 +4204,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6726,8 +6726,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7197,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V67" s="9" t="n">
         <v>0</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8251,8 +8251,8 @@
       <c r="P78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" s="9" t="n">
-        <v>1</v>
+      <c r="Q78" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>1</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9636,8 +9636,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9733,8 +9733,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="9" t="n">
         <v>0</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10677,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11091,8 +11091,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1597042</v>
+        <v>28680715</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Everyone Belongs</t>
+          <t>City Speakers</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -11867,8 +11867,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -11886,15 +11886,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>4233</v>
+        <v>1597042</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Health Masters Toastmasters Club</t>
+          <t>Everyone Belongs</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -11953,19 +11953,19 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="10" t="n">
-        <v>5</v>
+      <c r="X116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,11 +11983,11 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>3679627</v>
+        <v>4233</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Healthy Living Toastmasters</t>
+          <t>Health Masters Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12035,13 +12035,13 @@
         <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T117" s="9" t="n">
         <v>0</v>
@@ -12050,13 +12050,13 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>3513</v>
+        <v>3679627</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>WPTM Communicators</t>
+          <t>Healthy Living Toastmasters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12147,19 +12147,19 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="9" t="n">
-        <v>0</v>
+      <c r="X118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12173,15 +12173,15 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1494</v>
+        <v>3513</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Bow Valley Toastmasters Club</t>
+          <t>WPTM Communicators</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -12244,13 +12244,13 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="10" t="n">
-        <v>6</v>
+      <c r="X119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28678543</v>
+        <v>1494</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Bow Valley Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,25 +12296,25 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L120" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
@@ -12334,11 +12334,11 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V120" s="9" t="n">
         <v>0</v>
@@ -12346,17 +12346,17 @@
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>0</v>
+      <c r="X120" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>8410</v>
+        <v>28678543</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Heritage Go-Getters Toastmasters Club</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,25 +12393,25 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K121" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O121" s="8" t="inlineStr">
@@ -12443,17 +12443,17 @@
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="10" t="n">
-        <v>5</v>
+      <c r="X121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -12468,11 +12468,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28675565</v>
+        <v>8410</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Southern Alberta Mandarin English (SAME) Club</t>
+          <t>Heritage Go-Getters Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>667</v>
+        <v>28675565</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Twin Rivers Club</t>
+          <t>Southern Alberta Mandarin English (SAME) Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>1</v>
@@ -12637,8 +12637,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>3</v>
+      <c r="X123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12658,19 +12658,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>6474352</v>
+        <v>667</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Cranston Communicators</t>
+          <t>Twin Rivers Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12722,20 +12722,20 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="10" t="n">
-        <v>1</v>
+      <c r="T124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>708</v>
+        <v>6474352</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Current Speakers Club</t>
+          <t>Cranston Communicators</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -12819,20 +12819,20 @@
       <c r="S125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1936</v>
+        <v>708</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Glenmore R.S.V.P. Club</t>
+          <t>Current Speakers Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -12922,14 +12922,14 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="10" t="n">
-        <v>4</v>
+      <c r="V126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X126" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="X126" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12953,15 +12953,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>976708</v>
+        <v>1936</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>MVP Advanced</t>
+          <t>Glenmore R.S.V.P. Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q127" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13013,20 +13013,20 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U127" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V127" s="9" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="X127" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13041,24 +13041,24 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>8091</v>
+        <v>976708</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Christian Toastmasters</t>
+          <t>MVP Advanced</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13099,13 +13099,13 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
         <v>0</v>
@@ -13113,17 +13113,17 @@
       <c r="T128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="U128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>6110</v>
+        <v>8091</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Garden of Voices Toastmasters</t>
+          <t>Christian Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13207,14 +13207,14 @@
       <c r="S129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,11 +13244,11 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>4472443</v>
+        <v>6110</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Latino Canadian Entrepreneurs</t>
+          <t>Garden of Voices Toastmasters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -13316,8 +13316,8 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
+      <c r="X130" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>6901</v>
+        <v>4472443</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Pursuers Club</t>
+          <t>Latino Canadian Entrepreneurs</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13401,26 +13401,26 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="10" t="n">
-        <v>7</v>
+      <c r="X131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2897</v>
+        <v>6901</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Speak Yourself Toastmasters</t>
+          <t>Pursuers Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>1</v>
@@ -13496,10 +13496,10 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
@@ -13516,8 +13516,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>2478</v>
+        <v>2897</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>The Y Club</t>
+          <t>Speak Yourself Toastmasters</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -13586,35 +13586,35 @@
       <c r="P133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" s="10" t="n">
-        <v>2</v>
+      <c r="Q133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13628,19 +13628,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>7022</v>
+        <v>2478</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Attitude Boosters Club</t>
+          <t>The Y Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,17 +13654,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
@@ -13683,8 +13683,8 @@
       <c r="P134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" s="9" t="n">
-        <v>0</v>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -13692,8 +13692,8 @@
       <c r="S134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -13704,14 +13704,14 @@
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>2</v>
+      <c r="X134" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -13729,11 +13729,11 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>7346209</v>
+        <v>7022</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CN Tower Toastmasters Club</t>
+          <t>Attitude Boosters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
@@ -13796,13 +13796,13 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="10" t="n">
-        <v>5</v>
+      <c r="X135" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>712844</v>
+        <v>7346209</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Money Talkers</t>
+          <t>CN Tower Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13862,11 +13862,11 @@
         </is>
       </c>
       <c r="M136" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O136" s="8" t="inlineStr">
@@ -13886,29 +13886,29 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
+      <c r="X136" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -13923,11 +13923,11 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>323</v>
+        <v>712844</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Oxbridge Orators Toastmasters Club</t>
+          <t>Money Talkers</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>0</v>
@@ -13959,11 +13959,11 @@
         </is>
       </c>
       <c r="M137" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O137" s="8" t="inlineStr">
@@ -13995,8 +13995,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="10" t="n">
-        <v>5</v>
+      <c r="X137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14004,8 +14004,8 @@
       <c r="Z137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA137" s="10" t="n">
-        <v>1</v>
+      <c r="AA137" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -14020,11 +14020,11 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>6097</v>
+        <v>323</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Paragon Toastmasters Club</t>
+          <t>Oxbridge Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14093,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14113,19 +14113,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2161</v>
+        <v>6097</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Bowmen Club</t>
+          <t>Paragon Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -14184,19 +14184,19 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14214,11 +14214,11 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>4023462</v>
+        <v>2161</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Fort Saskatchewan Toastmasters Club</t>
+          <t>Bowmen Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
@@ -14281,13 +14281,13 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>1</v>
+      <c r="X140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>8364</v>
+        <v>4023462</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Forward Thinkers Club</t>
+          <t>Fort Saskatchewan Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="7" t="n">
@@ -14378,19 +14378,19 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X141" s="10" t="n">
-        <v>6</v>
+      <c r="X141" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14408,11 +14408,11 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>5066</v>
+        <v>8364</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Morning Challengers Toastmasters Club</t>
+          <t>Forward Thinkers Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K142" s="4" t="n">
         <v>2</v>
@@ -14457,16 +14457,16 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" s="9" t="n">
         <v>0</v>
@@ -14481,7 +14481,7 @@
         <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14505,11 +14505,11 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>7223181</v>
+        <v>5066</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Scotford Toastmasters Club</t>
+          <t>Morning Challengers Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>1</v>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -14572,13 +14572,13 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="9" t="n">
-        <v>2</v>
+      <c r="X143" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -14598,15 +14598,15 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>6053</v>
+        <v>7223181</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>City Lights Club</t>
+          <t>Scotford Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -14627,10 +14627,10 @@
         <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
@@ -14654,13 +14654,13 @@
         <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" s="9" t="n">
         <v>0</v>
@@ -14669,13 +14669,13 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" s="10" t="n">
-        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>652</v>
+        <v>6053</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Club Bilingue D'Edmonton Toastmasters Club</t>
+          <t>City Lights Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145" s="9" t="n">
         <v>0</v>
@@ -14766,19 +14766,19 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>2</v>
+      <c r="X145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -14796,11 +14796,11 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>4699</v>
+        <v>652</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Confidence Builders Club</t>
+          <t>Club Bilingue D'Edmonton Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -14818,10 +14818,10 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>0</v>
@@ -14868,8 +14868,8 @@
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="10" t="n">
-        <v>4</v>
+      <c r="X146" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -14893,11 +14893,11 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28679490</v>
+        <v>4699</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>MicMasters at Bantrel</t>
+          <t>Confidence Builders Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="7" t="n">
@@ -14960,13 +14960,13 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
+      <c r="X147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -14990,11 +14990,11 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1022113</v>
+        <v>28679490</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Roasted To Toasted</t>
+          <t>MicMasters at Bantrel</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -15039,10 +15039,10 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15057,13 +15057,13 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="10" t="n">
-        <v>4</v>
+      <c r="X148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15087,11 +15087,11 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>3684</v>
+        <v>1022113</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Southern Lights Club</t>
+          <t>Roasted To Toasted</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -15109,17 +15109,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="7" t="n">
@@ -15136,16 +15136,16 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" s="9" t="n">
         <v>0</v>
@@ -15154,13 +15154,13 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -15175,24 +15175,24 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>939</v>
+        <v>3684</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Dunvegan Toastmasters</t>
+          <t>Southern Lights Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -15251,19 +15251,19 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X150" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15281,11 +15281,11 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>6450</v>
+        <v>939</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Grande Prairie Lunch Rappers Club</t>
+          <t>Dunvegan Toastmasters</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -15303,10 +15303,10 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
         <v>0</v>
@@ -15354,7 +15354,7 @@
         <v>0</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>6772</v>
+        <v>6450</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Peace Challengers Toastmasters Club</t>
+          <t>Grande Prairie Lunch Rappers Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -15400,10 +15400,10 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K152" s="4" t="n">
         <v>0</v>
@@ -15450,8 +15450,8 @@
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X152" s="9" t="n">
-        <v>0</v>
+      <c r="X152" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -15475,11 +15475,11 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28676401</v>
+        <v>6772</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>World Lights</t>
+          <t>Peace Challengers Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -15500,10 +15500,10 @@
         <v>9</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="8" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -15542,13 +15542,13 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X153" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15568,19 +15568,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1668231</v>
+        <v>28676401</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Chrysalis Social Butterflies</t>
+          <t>World Lights</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" s="8" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -15639,19 +15639,19 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="10" t="n">
-        <v>1</v>
+      <c r="Z154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15669,15 +15669,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>28679129</v>
+        <v>1668231</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>CISE Toastmasters Club</t>
+          <t>Chrysalis Social Butterflies</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,17 +15691,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K155" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
@@ -15741,14 +15741,14 @@
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X155" s="9" t="n">
-        <v>3</v>
+      <c r="X155" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15766,11 +15766,11 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>3650</v>
+        <v>28679129</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Power Speakers Club</t>
+          <t>CISE Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -15788,17 +15788,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L156" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M156" s="7" t="n">
@@ -15833,13 +15833,13 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X156" s="10" t="n">
-        <v>4</v>
+      <c r="X156" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -15863,11 +15863,11 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>2291</v>
+        <v>3650</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>TNT Toastmasters</t>
+          <t>Power Speakers Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -15921,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="S157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" s="9" t="n">
         <v>0</v>
@@ -15930,13 +15930,13 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -15960,15 +15960,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>5710</v>
+        <v>2291</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>WeBA Toastmasters Club</t>
+          <t>TNT Toastmasters</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K158" s="4" t="n">
         <v>0</v>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16018,7 +16018,7 @@
         <v>0</v>
       </c>
       <c r="S158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T158" s="9" t="n">
         <v>0</v>
@@ -16032,14 +16032,14 @@
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="9" t="n">
-        <v>1</v>
+      <c r="X158" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -16057,15 +16057,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>9220</v>
+        <v>5710</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Wood Buffalo Toastmasters Club</t>
+          <t>WeBA Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,10 +16079,10 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K159" s="4" t="n">
         <v>0</v>
@@ -16117,8 +16117,8 @@
       <c r="S159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T159" s="10" t="n">
-        <v>1</v>
+      <c r="T159" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U159" s="9" t="n">
         <v>0</v>
@@ -16129,8 +16129,8 @@
       <c r="W159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X159" s="10" t="n">
-        <v>5</v>
+      <c r="X159" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
@@ -16150,15 +16150,15 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>3423</v>
+        <v>9220</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Brownlee's Best Club</t>
+          <t>Wood Buffalo Toastmasters Club</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K160" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -16206,7 +16206,7 @@
         <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -16227,7 +16227,7 @@
         <v>0</v>
       </c>
       <c r="X160" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
@@ -16251,15 +16251,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>5143</v>
+        <v>3423</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Dawnbreakers Toastmasters</t>
+          <t>Brownlee's Best Club</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16273,17 +16273,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K161" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L161" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M161" s="7" t="n">
@@ -16300,10 +16300,10 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -16311,8 +16311,8 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
@@ -16324,13 +16324,13 @@
         <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -16348,15 +16348,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>6436</v>
+        <v>5143</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Fabulous Facilitators Club</t>
+          <t>Dawnbreakers Toastmasters</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
@@ -16406,28 +16406,28 @@
         <v>0</v>
       </c>
       <c r="S162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T162" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="10" t="n">
-        <v>2</v>
+      <c r="Z162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -16445,15 +16445,15 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>4939</v>
+        <v>6436</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>N'Orators Toastmasters Club</t>
+          <t>Fabulous Facilitators Club</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="S163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="9" t="n">
         <v>0</v>
@@ -16524,7 +16524,7 @@
         <v>0</v>
       </c>
       <c r="Z163" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -16542,11 +16542,11 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>284</v>
+        <v>4939</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Norwood Toastmasters Club</t>
+          <t>N'Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -16609,13 +16609,13 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X164" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
@@ -16639,15 +16639,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>1084</v>
+        <v>284</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Peter Kossowan's Communicators</t>
+          <t>Norwood Toastmasters Club</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16661,10 +16661,10 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K165" s="4" t="n">
         <v>0</v>
@@ -16712,13 +16712,13 @@
         <v>0</v>
       </c>
       <c r="X165" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -16732,19 +16732,19 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>4966</v>
+        <v>1084</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Aimcrier Toastmasters Club</t>
+          <t>Peter Kossowan's Communicators</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -16758,17 +16758,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K166" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="7" t="n">
@@ -16814,8 +16814,8 @@
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="10" t="n">
-        <v>1</v>
+      <c r="Z166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA166" s="10" t="n">
         <v>1</v>
@@ -16833,11 +16833,11 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>9386</v>
+        <v>4966</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Athabasca Landing Toastmasters Club</t>
+          <t>Aimcrier Toastmasters Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
@@ -16855,17 +16855,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K167" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L167" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
@@ -16893,8 +16893,8 @@
       <c r="S167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T167" s="10" t="n">
-        <v>1</v>
+      <c r="T167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U167" s="9" t="n">
         <v>0</v>
@@ -16905,14 +16905,14 @@
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X167" s="9" t="n">
-        <v>3</v>
+      <c r="X167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="10" t="n">
         <v>1</v>
@@ -16930,15 +16930,15 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1339804</v>
+        <v>9386</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Core Development</t>
+          <t>Athabasca Landing Toastmasters Club</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -16990,8 +16990,8 @@
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="9" t="n">
-        <v>0</v>
+      <c r="T168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
@@ -17003,7 +17003,7 @@
         <v>0</v>
       </c>
       <c r="X168" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -17027,11 +17027,11 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>4533786</v>
+        <v>1339804</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Licensed To Speak Toastmasters Club</t>
+          <t>Core Development</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -17049,10 +17049,10 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
         <v>0</v>
@@ -17099,8 +17099,8 @@
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="10" t="n">
-        <v>4</v>
+      <c r="X169" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
@@ -17124,11 +17124,11 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1437</v>
+        <v>4533786</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Settlement On Sturgeon Club</t>
+          <t>Licensed To Speak Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -17146,10 +17146,10 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K170" s="4" t="n">
         <v>0</v>
@@ -17197,7 +17197,7 @@
         <v>0</v>
       </c>
       <c r="X170" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -17221,11 +17221,11 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>3826</v>
+        <v>1437</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Sundowners Toastmasters Club</t>
+          <t>Settlement On Sturgeon Club</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
@@ -17243,17 +17243,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L171" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="7" t="n">
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>0</v>
@@ -17279,7 +17279,7 @@
         <v>0</v>
       </c>
       <c r="S171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T171" s="9" t="n">
         <v>0</v>
@@ -17306,8 +17306,105 @@
         <v>1</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>3826</v>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Sundowners Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M172" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O172" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P172" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X172" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA172" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA171"/>
+  <autoFilter ref="A1:AA172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17394,7 +17491,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17427,7 +17524,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -17460,7 +17557,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17526,7 +17623,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -17559,7 +17656,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17592,7 +17689,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17625,7 +17722,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17691,7 +17788,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17790,7 +17887,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -17856,7 +17953,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17922,7 +18019,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17988,7 +18085,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18021,7 +18118,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18087,7 +18184,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18120,7 +18217,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -18153,7 +18250,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18186,7 +18283,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18216,16 +18313,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -18234,7 +18331,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -18252,7 +18349,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -18318,7 +18415,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -18351,7 +18448,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -18417,7 +18514,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18483,7 +18580,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -18549,7 +18646,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2623,16 +2623,16 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="10" t="n">
         <v>1</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3125,8 +3125,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4148,17 +4148,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4536,17 +4536,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="7" t="n">
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>7</v>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
@@ -5259,11 +5259,11 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>0</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X47" s="9" t="n">
         <v>1</v>
@@ -5312,17 +5312,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>2</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -5938,8 +5938,8 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>2</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="P63" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q63" s="10" t="n">
         <v>2</v>
@@ -6808,14 +6808,14 @@
       <c r="T63" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U63" s="9" t="n">
-        <v>0</v>
+      <c r="U63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V63" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7096,14 +7096,14 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7200,7 +7200,7 @@
         <v>5</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -7578,8 +7578,8 @@
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="9" t="n">
-        <v>1</v>
+      <c r="S71" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T71" s="10" t="n">
         <v>1</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>1</v>
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8266,8 +8266,8 @@
       <c r="U78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -8610,17 +8610,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="7" t="n">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>-20</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9333,8 +9333,8 @@
       <c r="U89" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="7" t="n">
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10016,7 +10016,7 @@
         <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>5</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10103,8 +10103,8 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="7" t="n">
@@ -10191,8 +10191,8 @@
       <c r="P98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" s="9" t="n">
-        <v>1</v>
+      <c r="Q98" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12140,8 +12140,8 @@
       <c r="S118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -12528,14 +12528,14 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12825,11 +12825,11 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>3</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>5</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X127" s="9" t="n">
         <v>3</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="10" t="n">
         <v>1</v>
@@ -13117,7 +13117,7 @@
         <v>2</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" s="10" t="n">
         <v>1</v>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
@@ -13795,8 +13795,8 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" s="10" t="n">
         <v>1</v>
@@ -13893,7 +13893,7 @@
         <v>1</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L137" s="8" t="inlineStr">
         <is>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" s="9" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -14565,8 +14565,8 @@
       <c r="S143" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -14765,8 +14765,8 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>3</v>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="8" t="inlineStr">
         <is>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L151" s="8" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L153" s="8" t="inlineStr">
         <is>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="8" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
@@ -16217,11 +16217,11 @@
       <c r="T160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U160" s="9" t="n">
-        <v>0</v>
+      <c r="U160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -16273,17 +16273,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L161" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M161" s="7" t="n">
@@ -16318,7 +16318,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L163" s="8" t="inlineStr">
         <is>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L165" s="8" t="inlineStr">
         <is>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -16855,17 +16855,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="V167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L168" s="8" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L170" s="8" t="inlineStr">
         <is>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17340,17 +17340,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M172" s="7" t="n">
@@ -17384,11 +17384,11 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>0</v>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>5</v>
@@ -17590,7 +17590,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17638,7 +17638,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -17704,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -17737,7 +17737,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -17755,7 +17755,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -17821,7 +17821,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17887,7 +17887,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -17902,7 +17902,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -17920,7 +17920,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17935,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -17953,13 +17953,13 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -17968,7 +17968,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -18001,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -18019,13 +18019,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -18067,7 +18067,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -18085,7 +18085,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -18151,7 +18151,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -18166,7 +18166,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -18316,7 +18316,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -18364,7 +18364,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -18382,7 +18382,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18448,7 +18448,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -18463,7 +18463,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -18481,7 +18481,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -18496,7 +18496,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -18514,7 +18514,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18529,7 +18529,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -18580,7 +18580,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -18628,7 +18628,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -18646,7 +18646,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -18661,7 +18661,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2549,8 +2549,8 @@
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X19" s="9" t="n">
-        <v>3</v>
+      <c r="X19" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -3131,8 +3131,8 @@
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>3</v>
+      <c r="X25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="9" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -3992,8 +3992,8 @@
       <c r="S34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4192,8 +4192,8 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>2</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4371,8 +4371,8 @@
       <c r="P38" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
+      <c r="Q38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4974,8 +4974,8 @@
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X44" s="9" t="n">
-        <v>2</v>
+      <c r="X44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5059,8 +5059,8 @@
       <c r="S45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
+      <c r="T45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5438,8 +5438,8 @@
       <c r="P49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" s="9" t="n">
-        <v>1</v>
+      <c r="Q49" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6020,8 +6020,8 @@
       <c r="P55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" s="9" t="n">
-        <v>1</v>
+      <c r="Q55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8072,8 +8072,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>2</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>1</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -9721,11 +9721,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>3</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -10195,7 +10195,7 @@
         <v>2</v>
       </c>
       <c r="R98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" s="9" t="n">
         <v>1</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -10794,8 +10794,8 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>3</v>
+      <c r="X104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -12734,8 +12734,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>3</v>
+      <c r="X124" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13698,11 +13698,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>3</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>6</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
@@ -15250,8 +15250,8 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>2</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="8" t="inlineStr">
         <is>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>0</v>
       </c>
       <c r="Q165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="X166" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
@@ -16906,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -17002,8 +17002,8 @@
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>3</v>
+      <c r="X168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -17370,7 +17370,7 @@
         <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
@@ -17656,7 +17656,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17689,7 +17689,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17755,7 +17755,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17788,7 +17788,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17821,7 +17821,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18118,7 +18118,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18415,7 +18415,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -18514,7 +18514,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/208/inyear.xlsx
+++ b/docs/d/208/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5606,10 +5606,10 @@
         <v>10</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>-3</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6714,8 +6714,8 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>5</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -7966,8 +7966,8 @@
       <c r="R75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="9" t="n">
-        <v>1</v>
+      <c r="S75" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10871,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11550,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11558,8 +11558,8 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15244,8 +15244,8 @@
       <c r="S150" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U150" s="9" t="n">
         <v>0</v>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16891,7 +16891,7 @@
         <v>0</v>
       </c>
       <c r="S167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167" s="9" t="n">
         <v>0</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
@@ -17887,7 +17887,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -17986,7 +17986,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18283,7 +18283,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18514,7 +18514,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
